--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:43+00:00</t>
+    <t>2026-06-22T14:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant prescription</t>
+    <t>External ids for this request</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:38:01+00:00</t>
+    <t>2026-06-29T12:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5641" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5641" uniqueCount="887">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:42:10+00:00</t>
+    <t>2026-07-07T09:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,9 +663,6 @@
 An instance-order is an instantiation of a request or order and may be used to populate Medication Administration Record.  This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
-  </si>
-  <si>
-    <t>order</t>
   </si>
   <si>
     <t>The kind of medication order.</t>
@@ -1993,7 +1990,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260619134041</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -2672,7 +2669,7 @@
     <t>allowedCodeableConcept</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260619134042</t>
   </si>
   <si>
     <t>MedicationRequest.substitution.reason</t>
@@ -5171,7 +5168,7 @@
         <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>82</v>
@@ -5189,10 +5186,10 @@
         <v>186</v>
       </c>
       <c r="Y18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -5225,16 +5222,16 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -5242,10 +5239,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5271,13 +5268,13 @@
         <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -5306,11 +5303,11 @@
         <v>198</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Z19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
       </c>
@@ -5327,7 +5324,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -5345,13 +5342,13 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -5359,10 +5356,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5388,10 +5385,10 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5421,11 +5418,11 @@
         <v>186</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
       </c>
@@ -5442,7 +5439,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -5457,16 +5454,16 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -5474,10 +5471,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5500,16 +5497,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5559,7 +5556,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5580,7 +5577,7 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>82</v>
@@ -5591,10 +5588,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5617,13 +5614,13 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5674,7 +5671,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5695,7 +5692,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5706,10 +5703,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5732,16 +5729,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5770,11 +5767,11 @@
         <v>198</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>246</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5791,7 +5788,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>91</v>
@@ -5806,27 +5803,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5849,16 +5846,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5908,7 +5905,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -5923,27 +5920,27 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5966,16 +5963,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -6025,7 +6022,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -6040,27 +6037,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6083,13 +6080,13 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6140,7 +6137,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6155,16 +6152,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -6172,10 +6169,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6198,13 +6195,13 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6255,7 +6252,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -6270,27 +6267,27 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6313,13 +6310,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6370,7 +6367,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -6385,16 +6382,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -6402,10 +6399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6428,13 +6425,13 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6485,7 +6482,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6500,16 +6497,16 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6517,10 +6514,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6546,13 +6543,13 @@
         <v>194</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6581,11 +6578,11 @@
         <v>198</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6602,7 +6599,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6617,13 +6614,13 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
@@ -6634,10 +6631,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6660,13 +6657,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6717,7 +6714,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6738,10 +6735,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6749,10 +6746,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6778,13 +6775,13 @@
         <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6813,11 +6810,11 @@
         <v>198</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6834,7 +6831,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6849,27 +6846,27 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6892,16 +6889,16 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6939,7 +6936,7 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6949,7 +6946,7 @@
         <v>140</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6964,16 +6961,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6981,13 +6978,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>82</v>
@@ -7009,16 +7006,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="N34" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7068,7 +7065,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -7083,16 +7080,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -7100,13 +7097,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>82</v>
@@ -7128,16 +7125,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="M35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7187,7 +7184,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -7202,16 +7199,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -7219,13 +7216,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
@@ -7247,16 +7244,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7306,7 +7303,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7321,16 +7318,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -7338,10 +7335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7364,13 +7361,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7421,7 +7418,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7436,13 +7433,13 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
@@ -7453,10 +7450,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7482,10 +7479,10 @@
         <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7536,7 +7533,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7557,7 +7554,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -7568,10 +7565,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7594,13 +7591,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7651,7 +7648,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7666,13 +7663,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -7683,10 +7680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7712,14 +7709,14 @@
         <v>173</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7768,7 +7765,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7783,13 +7780,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7800,10 +7797,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7829,13 +7826,13 @@
         <v>194</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7864,11 +7861,11 @@
         <v>198</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7885,7 +7882,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7906,7 +7903,7 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -7917,10 +7914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7943,13 +7940,13 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8000,7 +7997,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -8015,13 +8012,13 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -8032,10 +8029,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8058,13 +8055,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8115,7 +8112,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8130,13 +8127,13 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -8147,10 +8144,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8173,16 +8170,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8232,7 +8229,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8247,13 +8244,13 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -8264,10 +8261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8290,13 +8287,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8347,28 +8344,28 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -8379,10 +8376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8408,10 +8405,10 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>169</v>
@@ -8455,7 +8452,7 @@
         <v>139</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
@@ -8464,7 +8461,7 @@
         <v>140</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8485,7 +8482,7 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -8496,14 +8493,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8525,10 +8522,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>169</v>
@@ -8583,7 +8580,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8615,10 +8612,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8641,17 +8638,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8700,7 +8697,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8721,21 +8718,21 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8758,17 +8755,17 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8817,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8838,21 +8835,21 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8878,16 +8875,16 @@
         <v>194</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8915,16 +8912,16 @@
         <v>198</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8934,7 +8931,7 @@
         <v>140</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8955,24 +8952,24 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
@@ -8997,16 +8994,16 @@
         <v>194</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9034,11 +9031,11 @@
         <v>198</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
       </c>
@@ -9055,7 +9052,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9076,21 +9073,21 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9113,13 +9110,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9170,28 +9167,28 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
@@ -9202,10 +9199,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9231,10 +9228,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>169</v>
@@ -9278,7 +9275,7 @@
         <v>139</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
@@ -9287,7 +9284,7 @@
         <v>140</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9308,7 +9305,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -9319,10 +9316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9345,19 +9342,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9367,46 +9364,46 @@
         <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9427,21 +9424,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9464,19 +9461,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9525,7 +9522,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9546,24 +9543,24 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>82</v>
@@ -9588,16 +9585,16 @@
         <v>194</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9625,11 +9622,11 @@
         <v>198</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9646,7 +9643,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9667,21 +9664,21 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9704,13 +9701,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9761,28 +9758,28 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9793,10 +9790,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9822,10 +9819,10 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>169</v>
@@ -9869,7 +9866,7 @@
         <v>139</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
@@ -9878,7 +9875,7 @@
         <v>140</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9899,7 +9896,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9910,10 +9907,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9936,19 +9933,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9997,7 +9994,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10018,21 +10015,21 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10055,19 +10052,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -10077,7 +10074,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -10116,7 +10113,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10137,21 +10134,21 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10174,13 +10171,13 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10231,7 +10228,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10252,21 +10249,21 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10289,19 +10286,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -10350,7 +10347,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10371,7 +10368,7 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -10382,10 +10379,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10408,13 +10405,13 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10465,28 +10462,28 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -10497,10 +10494,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10526,10 +10523,10 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>169</v>
@@ -10573,7 +10570,7 @@
         <v>139</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
@@ -10582,7 +10579,7 @@
         <v>140</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10603,7 +10600,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -10614,14 +10611,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10643,10 +10640,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>169</v>
@@ -10701,7 +10698,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10733,10 +10730,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10759,17 +10756,17 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10818,7 +10815,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10839,7 +10836,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10850,10 +10847,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10876,17 +10873,17 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10935,28 +10932,28 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10967,10 +10964,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10993,13 +10990,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11050,28 +11047,28 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -11082,10 +11079,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11111,10 +11108,10 @@
         <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>169</v>
@@ -11158,7 +11155,7 @@
         <v>139</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
@@ -11167,7 +11164,7 @@
         <v>140</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11188,7 +11185,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -11199,10 +11196,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11225,13 +11222,13 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11270,7 +11267,7 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
@@ -11280,7 +11277,7 @@
         <v>140</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11301,7 +11298,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -11312,13 +11309,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>82</v>
@@ -11340,13 +11337,13 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="M71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11397,7 +11394,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11418,7 +11415,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -11429,10 +11426,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11455,13 +11452,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11512,28 +11509,28 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -11544,10 +11541,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11573,10 +11570,10 @@
         <v>136</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>169</v>
@@ -11620,7 +11617,7 @@
         <v>139</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
@@ -11629,7 +11626,7 @@
         <v>140</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11650,7 +11647,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11661,10 +11658,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11687,16 +11684,16 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11746,16 +11743,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI74" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11767,21 +11764,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11804,69 +11801,69 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="R75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
@@ -11874,7 +11871,7 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>103</v>
@@ -11886,21 +11883,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>530</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11923,19 +11920,19 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11984,7 +11981,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12005,7 +12002,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -12016,10 +12013,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12042,13 +12039,13 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12099,7 +12096,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12120,7 +12117,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -12131,10 +12128,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12157,19 +12154,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -12218,7 +12215,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12239,7 +12236,7 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -12250,10 +12247,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12276,19 +12273,19 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="N79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12337,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12358,7 +12355,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -12369,10 +12366,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12398,10 +12395,10 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12431,28 +12428,28 @@
         <v>186</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="Z80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12473,7 +12470,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -12484,10 +12481,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12510,13 +12507,13 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12524,52 +12521,52 @@
         <v>82</v>
       </c>
       <c r="Q81" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="R81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="R81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12590,7 +12587,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -12601,10 +12598,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12627,13 +12624,13 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12684,7 +12681,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12705,7 +12702,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12716,10 +12713,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12742,13 +12739,13 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12799,7 +12796,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12820,7 +12817,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12831,10 +12828,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12857,13 +12854,13 @@
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12914,7 +12911,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12935,7 +12932,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12946,10 +12943,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12975,10 +12972,10 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13008,11 +13005,11 @@
         <v>186</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
@@ -13029,7 +13026,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13050,7 +13047,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -13061,10 +13058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13090,13 +13087,13 @@
         <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13126,25 +13123,25 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13165,7 +13162,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -13176,10 +13173,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13202,16 +13199,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13261,7 +13258,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13282,7 +13279,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -13293,10 +13290,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13322,16 +13319,16 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13359,28 +13356,28 @@
         <v>186</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13401,7 +13398,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -13412,10 +13409,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13438,13 +13435,13 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13495,7 +13492,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13516,7 +13513,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -13527,10 +13524,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13556,13 +13553,13 @@
         <v>194</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13591,28 +13588,28 @@
         <v>115</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="Z90" t="s" s="2">
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13633,7 +13630,7 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
@@ -13644,10 +13641,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13670,16 +13667,16 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13708,28 +13705,28 @@
         <v>198</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13750,21 +13747,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13790,16 +13787,16 @@
         <v>194</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13824,29 +13821,29 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13867,21 +13864,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>635</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13907,14 +13904,14 @@
         <v>194</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13939,29 +13936,29 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13982,21 +13979,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>643</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14022,16 +14019,16 @@
         <v>194</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14059,28 +14056,28 @@
         <v>198</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="Z94" t="s" s="2">
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14101,21 +14098,21 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>653</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14138,13 +14135,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14195,7 +14192,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14222,15 +14219,15 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14253,13 +14250,13 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14310,28 +14307,28 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -14342,10 +14339,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14371,10 +14368,10 @@
         <v>136</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>169</v>
@@ -14418,7 +14415,7 @@
         <v>139</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
@@ -14427,7 +14424,7 @@
         <v>140</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14448,7 +14445,7 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
@@ -14459,10 +14456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14488,14 +14485,14 @@
         <v>194</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14523,28 +14520,28 @@
         <v>198</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14571,15 +14568,15 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14602,19 +14599,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14651,7 +14648,7 @@
         <v>82</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
@@ -14661,7 +14658,7 @@
         <v>140</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14682,24 +14679,24 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>82</v>
@@ -14721,19 +14718,19 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="L100" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="M100" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14782,7 +14779,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14803,21 +14800,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14840,13 +14837,13 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14897,28 +14894,28 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14929,10 +14926,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14958,10 +14955,10 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>169</v>
@@ -15005,7 +15002,7 @@
         <v>139</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>82</v>
@@ -15014,7 +15011,7 @@
         <v>140</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15035,7 +15032,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
@@ -15046,10 +15043,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15072,16 +15069,16 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15131,7 +15128,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15152,21 +15149,21 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15189,16 +15186,16 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15248,7 +15245,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15269,21 +15266,21 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15306,19 +15303,19 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15355,7 +15352,7 @@
         <v>82</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
@@ -15365,7 +15362,7 @@
         <v>140</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15386,24 +15383,24 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>708</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>82</v>
@@ -15425,19 +15422,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M106" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15486,7 +15483,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15507,21 +15504,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>708</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15544,13 +15541,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15601,28 +15598,28 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
@@ -15633,10 +15630,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15662,10 +15659,10 @@
         <v>136</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>169</v>
@@ -15709,7 +15706,7 @@
         <v>139</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>82</v>
@@ -15718,7 +15715,7 @@
         <v>140</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15739,7 +15736,7 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
@@ -15750,10 +15747,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15776,16 +15773,16 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15835,7 +15832,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15856,21 +15853,21 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15893,16 +15890,16 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15952,7 +15949,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15973,21 +15970,21 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16010,19 +16007,19 @@
         <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16071,7 +16068,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16092,21 +16089,21 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO111" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>728</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16129,13 +16126,13 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16186,28 +16183,28 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
@@ -16218,10 +16215,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16247,10 +16244,10 @@
         <v>136</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>169</v>
@@ -16294,7 +16291,7 @@
         <v>139</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>82</v>
@@ -16303,7 +16300,7 @@
         <v>140</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16324,7 +16321,7 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>82</v>
@@ -16335,10 +16332,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16361,13 +16358,13 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16418,7 +16415,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16439,7 +16436,7 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
@@ -16450,10 +16447,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16476,13 +16473,13 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16533,7 +16530,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16554,7 +16551,7 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
@@ -16565,10 +16562,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16591,19 +16588,19 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16652,7 +16649,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16673,7 +16670,7 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
@@ -16684,10 +16681,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16710,17 +16707,17 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16769,7 +16766,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16790,7 +16787,7 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16801,10 +16798,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16827,13 +16824,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16884,7 +16881,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16902,10 +16899,10 @@
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AM118" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -16916,10 +16913,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16942,13 +16939,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16999,28 +16996,28 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>82</v>
@@ -17031,10 +17028,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17112,7 +17109,7 @@
         <v>140</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17144,13 +17141,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -17172,16 +17169,16 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17231,7 +17228,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17263,10 +17260,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17289,13 +17286,13 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17346,28 +17343,28 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -17378,10 +17375,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17452,7 +17449,7 @@
         <v>139</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>82</v>
@@ -17461,7 +17458,7 @@
         <v>140</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17493,10 +17490,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17522,13 +17519,13 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17536,49 +17533,49 @@
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>91</v>
@@ -17610,10 +17607,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17636,13 +17633,13 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17693,7 +17690,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17725,14 +17722,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17754,10 +17751,10 @@
         <v>136</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>169</v>
@@ -17812,7 +17809,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17844,10 +17841,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17870,16 +17867,16 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17929,7 +17926,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17950,7 +17947,7 @@
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17961,10 +17958,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17987,13 +17984,13 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18044,28 +18041,28 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -18076,10 +18073,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18105,10 +18102,10 @@
         <v>136</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>169</v>
@@ -18161,7 +18158,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18182,7 +18179,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18193,14 +18190,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18222,10 +18219,10 @@
         <v>136</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>169</v>
@@ -18280,7 +18277,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18312,10 +18309,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18338,13 +18335,13 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18395,7 +18392,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18416,7 +18413,7 @@
         <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
@@ -18427,10 +18424,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18453,13 +18450,13 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18510,7 +18507,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18531,7 +18528,7 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18542,10 +18539,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18568,13 +18565,13 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18625,7 +18622,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18646,7 +18643,7 @@
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
@@ -18657,10 +18654,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18683,19 +18680,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18744,7 +18741,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18762,10 +18759,10 @@
         <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
@@ -18776,10 +18773,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18802,16 +18799,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18861,7 +18858,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18879,24 +18876,24 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>816</v>
       </c>
-      <c r="AM135" t="s" s="2">
+      <c r="AN135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO135" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>818</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18919,13 +18916,13 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18976,7 +18973,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18994,24 +18991,24 @@
         <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="AM136" t="s" s="2">
+      <c r="AN136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO136" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>824</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19034,16 +19031,16 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>826</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19093,7 +19090,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19111,10 +19108,10 @@
         <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>829</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -19125,10 +19122,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19151,13 +19148,13 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>832</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>833</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19208,7 +19205,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19229,10 +19226,10 @@
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19240,10 +19237,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19266,13 +19263,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19323,7 +19320,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19341,10 +19338,10 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
@@ -19355,10 +19352,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19381,13 +19378,13 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19438,28 +19435,28 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -19470,10 +19467,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19499,10 +19496,10 @@
         <v>136</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>169</v>
@@ -19555,7 +19552,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19576,7 +19573,7 @@
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
@@ -19587,14 +19584,14 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19616,10 +19613,10 @@
         <v>136</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>169</v>
@@ -19674,7 +19671,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19706,10 +19703,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19732,16 +19729,16 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19770,16 +19767,16 @@
         <v>198</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>849</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -19789,7 +19786,7 @@
         <v>140</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>91</v>
@@ -19807,27 +19804,27 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AM143" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO143" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>851</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="C144" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>82</v>
@@ -19852,13 +19849,13 @@
         <v>194</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19888,7 +19885,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19906,7 +19903,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>91</v>
@@ -19924,24 +19921,24 @@
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AM144" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO144" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>851</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19967,10 +19964,10 @@
         <v>194</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20000,11 +19997,11 @@
         <v>198</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="Z145" t="s" s="2">
         <v>858</v>
       </c>
-      <c r="Z145" t="s" s="2">
-        <v>859</v>
-      </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
       </c>
@@ -20021,7 +20018,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20039,24 +20036,24 @@
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="AM145" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="AM145" t="s" s="2">
+      <c r="AN145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO145" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>862</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20079,13 +20076,13 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20136,28 +20133,28 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM146" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
@@ -20168,10 +20165,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20197,10 +20194,10 @@
         <v>136</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>169</v>
@@ -20244,7 +20241,7 @@
         <v>139</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>82</v>
@@ -20253,7 +20250,7 @@
         <v>140</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20274,7 +20271,7 @@
         <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
@@ -20285,10 +20282,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20311,19 +20308,19 @@
         <v>92</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20372,7 +20369,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20393,21 +20390,21 @@
         <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20430,19 +20427,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20491,7 +20488,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20512,21 +20509,21 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO149" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20549,13 +20546,13 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>869</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>870</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>871</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20606,7 +20603,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20621,13 +20618,13 @@
         <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20638,14 +20635,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -20664,16 +20661,16 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>876</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>877</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20723,7 +20720,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20744,7 +20741,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20755,10 +20752,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20781,16 +20778,16 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>882</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>883</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>884</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>885</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20840,7 +20837,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20855,13 +20852,13 @@
         <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>886</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:52:18+00:00</t>
+    <t>2026-07-16T13:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5153" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="857">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:43:45+00:00</t>
+    <t>2026-07-16T16:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1421,6 +1421,22 @@
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.timing.repeat.extension:AdditionalWhenValues</t>
+  </si>
+  <si>
+    <t>AdditionalWhenValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-additional-when-values|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>Codes additionnels pour l'occurrence, issus de PN13</t>
+  </si>
+  <si>
+    <t>Précise des codes additionnels pour la période d'occurrence qui ne sont pas dans le jeu de valeurs event-timing</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.bounds[x]</t>
@@ -2969,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO139"/>
+  <dimension ref="A1:AO140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.60546875" customWidth="true" bestFit="true"/>
@@ -9551,9 +9567,11 @@
         <v>448</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9571,16 +9589,16 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9619,29 +9637,31 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>453</v>
+        <v>388</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9650,7 +9670,7 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9661,14 +9681,12 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9689,13 +9707,13 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9734,19 +9752,17 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9767,7 +9783,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9778,12 +9794,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9801,16 +9819,16 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>462</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9861,7 +9879,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9873,7 +9891,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9882,7 +9900,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>383</v>
+        <v>459</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9893,21 +9911,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9919,17 +9937,15 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9966,31 +9982,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -10010,21 +10026,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -10033,19 +10049,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>386</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>467</v>
+        <v>169</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10083,31 +10099,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>388</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -10116,21 +10132,21 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>470</v>
+        <v>383</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10156,21 +10172,19 @@
         <v>277</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q62" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10214,7 +10228,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10223,7 +10237,7 @@
         <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>103</v>
@@ -10235,21 +10249,21 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10272,69 +10286,69 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
@@ -10342,7 +10356,7 @@
         <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
@@ -10354,21 +10368,21 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10391,16 +10405,20 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10469,7 +10487,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -10480,10 +10498,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10506,7 +10524,7 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>495</v>
@@ -10514,12 +10532,8 @@
       <c r="M65" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N65" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10567,7 +10581,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10588,7 +10602,7 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10599,10 +10613,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10625,19 +10639,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10707,7 +10721,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10718,10 +10732,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10744,16 +10758,20 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>499</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10777,31 +10795,31 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10822,7 +10840,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10833,10 +10851,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10859,66 +10877,64 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>482</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q68" t="s" s="2">
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10939,7 +10955,7 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10976,7 +10992,7 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>518</v>
@@ -10989,7 +11005,9 @@
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q69" s="2"/>
+      <c r="Q69" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="R69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11033,7 +11051,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11054,7 +11072,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -11065,10 +11083,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11091,13 +11109,13 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11148,7 +11166,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11169,7 +11187,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -11180,10 +11198,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11206,13 +11224,13 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11263,7 +11281,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11284,7 +11302,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -11295,10 +11313,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11321,13 +11339,13 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>499</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11354,13 +11372,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11378,7 +11396,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11399,7 +11417,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -11410,10 +11428,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11424,7 +11442,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11439,14 +11457,12 @@
         <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N73" t="s" s="2">
         <v>534</v>
       </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11473,33 +11489,35 @@
       <c r="X73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y73" s="2"/>
+      <c r="Y73" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="Z73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -11514,7 +11532,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>383</v>
+        <v>516</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11525,10 +11543,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11551,16 +11569,16 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11586,13 +11604,11 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11610,7 +11626,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11642,10 +11658,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11668,7 +11684,7 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>543</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>544</v>
@@ -11679,9 +11695,7 @@
       <c r="N75" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="O75" t="s" s="2">
-        <v>547</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11705,13 +11719,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11729,7 +11743,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11750,7 +11764,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>551</v>
+        <v>383</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11761,10 +11775,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11775,7 +11789,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11787,16 +11801,20 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>553</v>
+        <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11820,13 +11838,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11844,13 +11862,13 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -11865,7 +11883,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11876,10 +11894,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11902,7 +11920,7 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>194</v>
+        <v>558</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>559</v>
@@ -11910,9 +11928,7 @@
       <c r="M77" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>561</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11937,13 +11953,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11961,7 +11977,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11982,7 +11998,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11993,10 +12009,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12019,16 +12035,16 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>567</v>
+        <v>194</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12054,13 +12070,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -12078,7 +12094,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12099,21 +12115,21 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12136,20 +12152,18 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>194</v>
+        <v>572</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -12173,11 +12187,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12195,7 +12211,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12216,21 +12232,21 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12256,14 +12272,16 @@
         <v>194</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12288,11 +12306,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12310,7 +12328,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12331,21 +12349,21 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12371,16 +12389,14 @@
         <v>194</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12405,13 +12421,11 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12429,7 +12443,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12450,21 +12464,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12475,7 +12489,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12487,16 +12501,20 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>439</v>
+        <v>194</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12520,13 +12538,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12544,13 +12562,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12565,7 +12583,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12590,7 +12608,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12599,16 +12617,16 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>380</v>
+        <v>610</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>381</v>
+        <v>611</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12659,19 +12677,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>382</v>
+        <v>612</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12680,32 +12698,32 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12717,17 +12735,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12764,31 +12780,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12808,21 +12824,21 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12831,21 +12847,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>612</v>
+        <v>385</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12869,43 +12885,43 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>617</v>
+        <v>388</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12914,21 +12930,21 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12951,19 +12967,17 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>620</v>
+        <v>194</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12988,29 +13002,31 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC86" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13031,25 +13047,23 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13070,19 +13084,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O87" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13119,19 +13133,17 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13152,23 +13164,25 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13186,19 +13200,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>379</v>
+        <v>634</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>380</v>
+        <v>635</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>627</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13246,7 +13264,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>382</v>
+        <v>630</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13258,7 +13276,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13267,32 +13285,32 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>383</v>
+        <v>607</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -13304,17 +13322,15 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13351,31 +13367,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13395,21 +13411,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13418,19 +13434,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>637</v>
+        <v>136</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>638</v>
+        <v>385</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>639</v>
+        <v>386</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>640</v>
+        <v>169</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13468,31 +13484,31 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>641</v>
+        <v>388</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13501,21 +13517,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>470</v>
+        <v>383</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>642</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13538,16 +13554,16 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13597,7 +13613,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13618,21 +13634,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13640,7 +13656,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>91</v>
@@ -13655,20 +13671,18 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>655</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13704,17 +13718,19 @@
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC92" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13735,25 +13751,23 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>657</v>
+        <v>484</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13774,19 +13788,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>629</v>
+        <v>656</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13823,19 +13837,17 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13856,23 +13868,25 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13890,19 +13904,23 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>379</v>
+        <v>634</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>380</v>
+        <v>666</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>658</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>660</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13950,7 +13968,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>382</v>
+        <v>661</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13962,7 +13980,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13971,32 +13989,32 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>383</v>
+        <v>662</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>663</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -14008,17 +14026,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14055,31 +14071,31 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -14099,21 +14115,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -14122,19 +14138,19 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>637</v>
+        <v>136</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>638</v>
+        <v>385</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>639</v>
+        <v>386</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>640</v>
+        <v>169</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14172,31 +14188,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>641</v>
+        <v>388</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14205,21 +14221,21 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>470</v>
+        <v>383</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>642</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14242,16 +14258,16 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14301,7 +14317,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14322,21 +14338,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14344,7 +14360,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>91</v>
@@ -14359,20 +14375,18 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>672</v>
+        <v>650</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>673</v>
+        <v>651</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>675</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14420,7 +14434,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14441,21 +14455,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>677</v>
+        <v>484</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>678</v>
+        <v>654</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14475,19 +14489,23 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>379</v>
+        <v>676</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>380</v>
+        <v>677</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14535,7 +14553,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>382</v>
+        <v>681</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14547,7 +14565,7 @@
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14556,32 +14574,32 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>383</v>
+        <v>682</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>82</v>
+        <v>683</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14593,17 +14611,15 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14640,31 +14656,31 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14684,21 +14700,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14707,18 +14723,20 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>682</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>683</v>
+        <v>385</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14755,31 +14773,31 @@
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>685</v>
+        <v>388</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14788,7 +14806,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>686</v>
+        <v>383</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14799,10 +14817,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14825,7 +14843,7 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>688</v>
@@ -14925,7 +14943,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>91</v>
@@ -14940,7 +14958,7 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>693</v>
@@ -14948,12 +14966,8 @@
       <c r="M103" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>696</v>
-      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -15001,7 +15015,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15022,7 +15036,7 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -15033,10 +15047,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15059,17 +15073,19 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15118,7 +15134,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15139,7 +15155,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -15173,19 +15189,21 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15233,7 +15251,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15251,10 +15269,10 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>708</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
@@ -15265,10 +15283,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15291,13 +15309,13 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>379</v>
+        <v>710</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>380</v>
+        <v>711</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>381</v>
+        <v>712</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15348,7 +15366,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>382</v>
+        <v>709</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15360,16 +15378,16 @@
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>82</v>
+        <v>713</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>383</v>
+        <v>714</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
@@ -15380,10 +15398,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15394,7 +15412,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15406,13 +15424,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15451,29 +15469,31 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
@@ -15482,7 +15502,7 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
@@ -15493,14 +15513,12 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15509,7 +15527,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>82</v>
@@ -15521,17 +15539,15 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>714</v>
+        <v>136</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>715</v>
+        <v>137</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15568,16 +15584,14 @@
         <v>82</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>388</v>
@@ -15589,7 +15603,7 @@
         <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>142</v>
@@ -15612,12 +15626,14 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="B109" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15638,15 +15654,17 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>379</v>
+        <v>719</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>380</v>
+        <v>720</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15695,19 +15713,19 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15716,7 +15734,7 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15727,10 +15745,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15741,7 +15759,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15753,13 +15771,13 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15798,31 +15816,31 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15831,7 +15849,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15842,10 +15860,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15853,10 +15871,10 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15868,24 +15886,22 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>724</v>
+        <v>137</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>727</v>
+        <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>82</v>
@@ -15915,31 +15931,31 @@
         <v>82</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>728</v>
+        <v>388</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15948,7 +15964,7 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
@@ -15959,10 +15975,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15985,22 +16001,24 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M112" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>82</v>
+        <v>732</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>82</v>
@@ -16045,7 +16063,7 @@
         <v>733</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>91</v>
@@ -16054,7 +16072,7 @@
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16077,43 +16095,39 @@
         <v>734</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>136</v>
+        <v>365</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>391</v>
+        <v>736</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -16161,19 +16175,19 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>393</v>
+        <v>738</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16193,44 +16207,46 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>705</v>
+        <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>736</v>
+        <v>391</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>737</v>
+        <v>392</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -16278,19 +16294,19 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>735</v>
+        <v>393</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>82</v>
@@ -16299,7 +16315,7 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>739</v>
+        <v>134</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
@@ -16336,15 +16352,17 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>379</v>
+        <v>710</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>380</v>
+        <v>741</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>743</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16393,7 +16411,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>382</v>
+        <v>740</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16405,7 +16423,7 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
@@ -16414,7 +16432,7 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>383</v>
+        <v>744</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
@@ -16425,21 +16443,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16451,17 +16469,15 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16510,19 +16526,19 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>82</v>
@@ -16542,14 +16558,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>390</v>
+        <v>166</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16562,26 +16578,24 @@
         <v>82</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="O117" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16629,7 +16643,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16650,7 +16664,7 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16661,42 +16675,46 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>637</v>
+        <v>136</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>744</v>
+        <v>391</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16744,19 +16762,19 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>743</v>
+        <v>393</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
@@ -16765,7 +16783,7 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>746</v>
+        <v>134</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -16776,10 +16794,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16802,7 +16820,7 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>748</v>
+        <v>642</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>749</v>
@@ -16859,7 +16877,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16917,13 +16935,13 @@
         <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16995,7 +17013,7 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>82</v>
@@ -17006,10 +17024,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17032,20 +17050,16 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>457</v>
+        <v>753</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="O121" t="s" s="2">
         <v>759</v>
       </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17093,7 +17107,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17111,10 +17125,10 @@
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>760</v>
+        <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17125,10 +17139,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17151,18 +17165,20 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="N122" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
       </c>
@@ -17210,7 +17226,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17228,24 +17244,24 @@
         <v>82</v>
       </c>
       <c r="AL122" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="AM122" t="s" s="2">
-        <v>767</v>
-      </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>768</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17268,15 +17284,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="M123" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -17325,7 +17343,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17343,24 +17361,24 @@
         <v>82</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="AM123" t="s" s="2">
+      <c r="AN123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO123" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>774</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17383,17 +17401,15 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>748</v>
+        <v>642</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>778</v>
-      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17442,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17460,24 +17476,24 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO124" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17500,15 +17516,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="M125" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17557,7 +17575,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17575,13 +17593,13 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>82</v>
+        <v>784</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>785</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17600,7 +17618,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>91</v>
@@ -17615,13 +17633,13 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>705</v>
+        <v>787</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17690,13 +17708,13 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>789</v>
+        <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>790</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17715,7 +17733,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>91</v>
@@ -17730,13 +17748,13 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>379</v>
+        <v>710</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>380</v>
+        <v>792</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>381</v>
+        <v>793</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17787,7 +17805,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>382</v>
+        <v>791</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17799,16 +17817,16 @@
         <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>82</v>
+        <v>794</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>383</v>
+        <v>795</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17819,21 +17837,21 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
@@ -17845,17 +17863,15 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17904,19 +17920,19 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>82</v>
@@ -17936,14 +17952,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>390</v>
+        <v>166</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -17956,26 +17972,24 @@
         <v>82</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="O129" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18023,7 +18037,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18044,7 +18058,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18055,44 +18069,46 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>567</v>
+        <v>136</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>795</v>
+        <v>391</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>796</v>
+        <v>392</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18116,74 +18132,74 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>798</v>
+        <v>82</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>799</v>
+        <v>82</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC130" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>794</v>
+        <v>393</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>789</v>
+        <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>800</v>
+        <v>134</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>801</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>803</v>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>91</v>
@@ -18198,16 +18214,16 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>194</v>
+        <v>572</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18233,9 +18249,11 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="Z131" t="s" s="2">
         <v>804</v>
       </c>
@@ -18243,19 +18261,17 @@
         <v>82</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC131" s="2"/>
       <c r="AD131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>91</v>
@@ -18273,26 +18289,28 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>799</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>808</v>
+      </c>
       <c r="D132" t="s" s="2">
         <v>82</v>
       </c>
@@ -18316,12 +18334,14 @@
         <v>194</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>802</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18346,11 +18366,9 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>808</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
         <v>809</v>
       </c>
@@ -18370,10 +18388,10 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>91</v>
@@ -18388,24 +18406,24 @@
         <v>82</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18428,13 +18446,13 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>379</v>
+        <v>194</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>380</v>
+        <v>811</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>381</v>
+        <v>812</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18461,13 +18479,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>82</v>
+        <v>813</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>82</v>
+        <v>814</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18485,7 +18503,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>382</v>
+        <v>810</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18497,41 +18515,41 @@
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>82</v>
+        <v>815</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>383</v>
+        <v>816</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>82</v>
+        <v>817</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18543,17 +18561,15 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18590,31 +18606,31 @@
         <v>82</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>82</v>
@@ -18634,14 +18650,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18657,23 +18673,21 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>816</v>
+        <v>136</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>817</v>
+        <v>385</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>818</v>
+        <v>386</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>820</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -18709,19 +18723,19 @@
         <v>82</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>821</v>
+        <v>388</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18733,7 +18747,7 @@
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
@@ -18742,21 +18756,21 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>822</v>
+        <v>383</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>823</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18767,7 +18781,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18779,19 +18793,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>379</v>
+        <v>821</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="O136" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18840,13 +18854,13 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
@@ -18861,21 +18875,21 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18895,19 +18909,23 @@
         <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="O137" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="L137" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -18955,7 +18973,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18970,38 +18988,38 @@
         <v>103</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO137" t="s" s="2">
         <v>836</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>839</v>
+        <v>82</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -19013,17 +19031,15 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="L138" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>843</v>
-      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19072,13 +19088,13 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
@@ -19087,13 +19103,13 @@
         <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>82</v>
+        <v>841</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>82</v>
+        <v>815</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
@@ -19104,14 +19120,14 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>82</v>
+        <v>844</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19130,16 +19146,16 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>847</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>848</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19189,7 +19205,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19204,18 +19220,135 @@
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
         <v>850</v>
       </c>
-      <c r="AL139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM139" t="s" s="2">
+      <c r="B140" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K140" t="s" s="2">
         <v>851</v>
       </c>
-      <c r="AN139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO139" t="s" s="2">
+      <c r="L140" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO140" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>91</v>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5995" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5556" uniqueCount="884">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2196,68 +2196,14 @@
     <t>Dose à administrer</t>
   </si>
   <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseRange.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x].id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseRange.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x].extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseRange.low</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x].low</t>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseQuantity</t>
+  </si>
+  <si>
+    <t>doseQuantity</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
-  </si>
-  <si>
-    <t>Low limit</t>
-  </si>
-  <si>
-    <t>The low limit. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Range.low</t>
-  </si>
-  <si>
-    <t>NR.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseRange.high</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x].high</t>
-  </si>
-  <si>
-    <t>High limit</t>
-  </si>
-  <si>
-    <t>The high limit. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the high element is missing, the high boundary is not known.</t>
-  </si>
-  <si>
-    <t>Range.high</t>
-  </si>
-  <si>
-    <t>NR.2</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.dose[x]:doseQuantity</t>
-  </si>
-  <si>
-    <t>doseQuantity</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x]</t>
@@ -2299,30 +2245,6 @@
     <t>Rythme d'administration</t>
   </si>
   <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x]:rateRange.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x].id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x]:rateRange.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x].extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x]:rateRange.low</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x].low</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x]:rateRange.high</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.rate[x].high</t>
-  </si>
-  <si>
     <t>MedicationRequest.dosageInstruction.maxDosePerPeriod</t>
   </si>
   <si>
@@ -2349,46 +2271,6 @@
   </si>
   <si>
     <t>RXO-23, RXE-19</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.numerator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Numerator value</t>
-  </si>
-  <si>
-    <t>The value of the numerator.</t>
-  </si>
-  <si>
-    <t>Ratio.numerator</t>
-  </si>
-  <si>
-    <t>.numerator</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.denominator</t>
-  </si>
-  <si>
-    <t>Denominator value</t>
-  </si>
-  <si>
-    <t>The value of the denominator.</t>
-  </si>
-  <si>
-    <t>Ratio.denominator</t>
-  </si>
-  <si>
-    <t>.denominator</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.maxDosePerAdministration</t>
@@ -3189,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO162"/>
+  <dimension ref="A1:AO150"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.60546875" customWidth="true" bestFit="true"/>
@@ -9070,7 +8952,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -11049,7 +10931,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -15821,9 +15703,11 @@
         <v>700</v>
       </c>
       <c r="B109" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15841,19 +15725,23 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>168</v>
+        <v>702</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>169</v>
+        <v>689</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15901,7 +15789,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>171</v>
+        <v>694</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15913,7 +15801,7 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15922,32 +15810,32 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>172</v>
+        <v>670</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>82</v>
+        <v>695</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>703</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15956,21 +15844,23 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>136</v>
+        <v>704</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>421</v>
+        <v>705</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>422</v>
+        <v>706</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -16006,11 +15896,9 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
@@ -16018,19 +15906,19 @@
         <v>140</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>176</v>
+        <v>709</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -16039,29 +15927,31 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>172</v>
+        <v>710</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>82</v>
+        <v>711</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>91</v>
@@ -16076,18 +15966,20 @@
         <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -16135,7 +16027,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16156,7 +16048,7 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>536</v>
+        <v>710</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
@@ -16167,10 +16059,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16178,7 +16070,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>91</v>
@@ -16193,18 +16085,20 @@
         <v>92</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -16252,7 +16146,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16273,25 +16167,23 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>545</v>
+        <v>722</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>720</v>
-      </c>
+        <v>724</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>82</v>
       </c>
@@ -16312,19 +16204,19 @@
         <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>689</v>
+        <v>725</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>690</v>
+        <v>726</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>691</v>
+        <v>727</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>692</v>
+        <v>728</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16373,7 +16265,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>694</v>
+        <v>729</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16394,21 +16286,21 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16431,19 +16323,17 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16480,17 +16370,19 @@
         <v>82</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AC114" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16511,25 +16403,23 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>729</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>731</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16547,23 +16437,19 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>698</v>
+        <v>737</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>739</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16611,7 +16497,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16629,24 +16515,24 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>729</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16758,14 +16644,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16787,14 +16673,12 @@
         <v>136</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>421</v>
+        <v>137</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16833,9 +16717,7 @@
       <c r="AB117" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AC117" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16864,7 +16746,7 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16875,18 +16757,20 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>743</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>745</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>91</v>
@@ -16898,20 +16782,18 @@
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>706</v>
+        <v>746</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>707</v>
+        <v>747</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16960,19 +16842,19 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>710</v>
+        <v>176</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
@@ -16981,29 +16863,31 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>743</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>750</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>91</v>
@@ -17015,19 +16899,19 @@
         <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>706</v>
+        <v>751</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>714</v>
+        <v>752</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>715</v>
+        <v>753</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>716</v>
+        <v>754</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17077,19 +16961,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>717</v>
+        <v>176</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -17098,21 +16982,21 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>718</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17132,23 +17016,19 @@
         <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>742</v>
+        <v>168</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>743</v>
+        <v>169</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>746</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17196,7 +17076,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>747</v>
+        <v>171</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17208,7 +17088,7 @@
         <v>82</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>82</v>
@@ -17217,21 +17097,21 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>748</v>
+        <v>172</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>749</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17242,7 +17122,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>82</v>
@@ -17254,13 +17134,13 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17299,31 +17179,31 @@
         <v>82</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17332,7 +17212,7 @@
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17343,21 +17223,21 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17369,16 +17249,16 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>421</v>
+        <v>185</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17386,7 +17266,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>82</v>
+        <v>761</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>82</v>
@@ -17416,31 +17296,31 @@
         <v>82</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17449,7 +17329,7 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -17460,10 +17340,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17483,16 +17363,16 @@
         <v>82</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>753</v>
+        <v>413</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17543,7 +17423,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>756</v>
+        <v>194</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17564,7 +17444,7 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>757</v>
+        <v>134</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>82</v>
@@ -17575,42 +17455,46 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>753</v>
+        <v>136</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>759</v>
+        <v>452</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17658,19 +17542,19 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>761</v>
+        <v>454</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
@@ -17679,7 +17563,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>762</v>
+        <v>134</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17690,10 +17574,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17713,23 +17597,21 @@
         <v>82</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>767</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17777,7 +17659,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17798,7 +17680,7 @@
         <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17809,10 +17691,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17832,21 +17714,19 @@
         <v>82</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>706</v>
+        <v>168</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>771</v>
+        <v>169</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>772</v>
+        <v>170</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>773</v>
-      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17894,7 +17774,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>774</v>
+        <v>171</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17906,7 +17786,7 @@
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>82</v>
@@ -17915,7 +17795,7 @@
         <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>769</v>
+        <v>172</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17926,21 +17806,21 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
@@ -17952,15 +17832,17 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>776</v>
+        <v>136</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>777</v>
+        <v>421</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -18009,28 +17891,28 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>775</v>
+        <v>176</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>779</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>780</v>
+        <v>172</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -18041,42 +17923,46 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>169</v>
+        <v>452</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -18124,19 +18010,19 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>171</v>
+        <v>454</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>82</v>
@@ -18145,7 +18031,7 @@
         <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -18156,10 +18042,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18170,7 +18056,7 @@
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>82</v>
@@ -18182,13 +18068,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>136</v>
+        <v>702</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>137</v>
+        <v>776</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>138</v>
+        <v>777</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18227,29 +18113,31 @@
         <v>82</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC129" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>176</v>
+        <v>775</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
@@ -18258,7 +18146,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>82</v>
+        <v>778</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18269,14 +18157,12 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>784</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18297,13 +18183,13 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18354,19 +18240,19 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>176</v>
+        <v>779</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18375,7 +18261,7 @@
         <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>82</v>
+        <v>783</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
@@ -18386,14 +18272,12 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>789</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18414,17 +18298,15 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>793</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18473,19 +18355,19 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>176</v>
+        <v>784</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>82</v>
@@ -18494,7 +18376,7 @@
         <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>82</v>
+        <v>783</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
@@ -18505,10 +18387,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18531,16 +18413,20 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>168</v>
+        <v>523</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>169</v>
+        <v>788</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>789</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>791</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -18588,7 +18474,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>171</v>
+        <v>787</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18600,16 +18486,16 @@
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>82</v>
+        <v>792</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>172</v>
+        <v>793</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18620,10 +18506,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18634,7 +18520,7 @@
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>82</v>
@@ -18646,15 +18532,17 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>136</v>
+        <v>621</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>137</v>
+        <v>795</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>797</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18691,54 +18579,54 @@
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>176</v>
+        <v>794</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>82</v>
+        <v>798</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>82</v>
+        <v>799</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>82</v>
+        <v>800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18746,7 +18634,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>91</v>
@@ -18761,24 +18649,22 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>105</v>
+        <v>702</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>185</v>
+        <v>802</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>82</v>
@@ -18820,10 +18706,10 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>188</v>
+        <v>801</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>91</v>
@@ -18832,30 +18718,30 @@
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>82</v>
+        <v>804</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>134</v>
+        <v>805</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>82</v>
+        <v>806</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18863,7 +18749,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>91</v>
@@ -18878,15 +18764,17 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>413</v>
+        <v>780</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>810</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18935,7 +18823,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>194</v>
+        <v>807</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18953,10 +18841,10 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>82</v>
+        <v>811</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>134</v>
+        <v>812</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
@@ -18967,46 +18855,42 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>136</v>
+        <v>814</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>452</v>
+        <v>815</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -19054,19 +18938,19 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>454</v>
+        <v>813</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
@@ -19075,10 +18959,10 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>134</v>
+        <v>817</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -19086,10 +18970,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19112,17 +18996,15 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>776</v>
+        <v>737</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>809</v>
-      </c>
+        <v>820</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19171,7 +19053,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19189,10 +19071,10 @@
         <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>82</v>
+        <v>821</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -19203,10 +19085,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19318,10 +19200,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19435,10 +19317,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19554,10 +19436,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19565,7 +19447,7 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>91</v>
@@ -19580,15 +19462,17 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>706</v>
+        <v>635</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>828</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>829</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19613,34 +19497,32 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>82</v>
+        <v>830</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>82</v>
+        <v>831</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>91</v>
@@ -19655,26 +19537,28 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>82</v>
+        <v>821</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>82</v>
+        <v>833</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>826</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>835</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19695,15 +19579,17 @@
         <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>819</v>
+        <v>201</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>828</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>829</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19728,13 +19614,11 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>82</v>
+        <v>836</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19752,10 +19636,10 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>91</v>
@@ -19770,24 +19654,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>82</v>
+        <v>821</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>82</v>
+        <v>833</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19810,13 +19694,13 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>819</v>
+        <v>201</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19843,13 +19727,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>82</v>
+        <v>840</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>82</v>
+        <v>841</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19867,7 +19751,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19885,24 +19769,24 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>82</v>
+        <v>842</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>82</v>
+        <v>844</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19925,20 +19809,16 @@
         <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>523</v>
+        <v>168</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>827</v>
+        <v>169</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>830</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19986,7 +19866,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>826</v>
+        <v>171</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19998,16 +19878,16 @@
         <v>82</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>831</v>
+        <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>832</v>
+        <v>172</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>82</v>
@@ -20018,21 +19898,21 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>82</v>
@@ -20044,16 +19924,16 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>621</v>
+        <v>136</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>834</v>
+        <v>421</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>835</v>
+        <v>422</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>836</v>
+        <v>219</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20091,54 +19971,54 @@
         <v>82</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>833</v>
+        <v>176</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>837</v>
+        <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>838</v>
+        <v>172</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>839</v>
+        <v>82</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20149,7 +20029,7 @@
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>82</v>
@@ -20158,19 +20038,23 @@
         <v>82</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>706</v>
+        <v>848</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
+        <v>850</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>852</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
       </c>
@@ -20218,13 +20102,13 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>82</v>
@@ -20236,24 +20120,24 @@
         <v>82</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>843</v>
+        <v>82</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20273,21 +20157,23 @@
         <v>82</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>819</v>
+        <v>168</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>859</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>860</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20335,7 +20221,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20353,24 +20239,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>850</v>
+        <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>82</v>
+        <v>863</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20393,13 +20279,13 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20450,7 +20336,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20465,16 +20351,16 @@
         <v>103</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>82</v>
+        <v>868</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>82</v>
+        <v>842</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20482,21 +20368,21 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>82</v>
+        <v>871</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>82</v>
@@ -20508,15 +20394,17 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>776</v>
+        <v>872</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>875</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20565,13 +20453,13 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>82</v>
@@ -20583,10 +20471,10 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>860</v>
+        <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20597,10 +20485,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20611,7 +20499,7 @@
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
@@ -20623,15 +20511,17 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>168</v>
+        <v>878</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>169</v>
+        <v>879</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>880</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>881</v>
+      </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20680,1435 +20570,33 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>171</v>
+        <v>877</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>82</v>
+        <v>882</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>172</v>
+        <v>883</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AC153" s="2"/>
-      <c r="AD153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="D154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y154" s="2"/>
-      <c r="Z154" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="P159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
-      <c r="P160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>911</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="O161" s="2"/>
-      <c r="P161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>918</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>919</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="O162" s="2"/>
-      <c r="P162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>922</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO162" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
